--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_195_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_195_R20.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.9991</v>
+        <v>13.1205</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2402</v>
+        <v>8.327999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7589</v>
+        <v>4.7925</v>
       </c>
       <c r="G2" t="n">
         <v>8.2036</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4913</v>
+        <v>1.6127</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6948</v>
+        <v>0.7826</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7965</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.2201</v>
+        <v>11.0605</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0679</v>
+        <v>7.4715</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1522</v>
+        <v>3.589</v>
       </c>
       <c r="G3" t="n">
         <v>6.0838</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3482</v>
+        <v>0.4922</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5816</v>
+        <v>0.8219</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.3297</v>
       </c>
       <c r="V3" t="n">
         <v>2.3969</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5776</v>
+        <v>5.9117</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0016</v>
+        <v>3.6045</v>
       </c>
       <c r="F4" t="n">
-        <v>2.576</v>
+        <v>2.3072</v>
       </c>
       <c r="G4" t="n">
         <v>3.0026</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4153</v>
+        <v>1.7493</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0499</v>
+        <v>0.6528</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3654</v>
+        <v>1.0965</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.16</v>
+        <v>2.8409</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2019</v>
+        <v>-1.6555</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3619</v>
+        <v>4.4964</v>
       </c>
       <c r="G5" t="n">
         <v>-0.047</v>
@@ -844,13 +844,13 @@
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8109</v>
+        <v>-0.13</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5149</v>
+        <v>0.0316</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2961</v>
+        <v>-0.1617</v>
       </c>
       <c r="V5" t="n">
         <v>0.9304</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0772</v>
+        <v>1.7672</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.598</v>
+        <v>-1.2442</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6753</v>
+        <v>3.0113</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1445</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3892</v>
+        <v>0.3007</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2003</v>
+        <v>0.5364</v>
       </c>
       <c r="V6" t="n">
         <v>2.5387</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0968</v>
+        <v>-0.0475</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4092</v>
+        <v>-0.5272</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3123</v>
+        <v>0.4797</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6133</v>
+        <v>-0.6579</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.36</v>
+        <v>-0.3434</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7467</v>
+        <v>-0.3145</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.206</v>
+        <v>-0.7829</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9053</v>
+        <v>0.0035</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6993</v>
+        <v>-0.7863</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5927</v>
+        <v>0.1249</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4547</v>
+        <v>-0.3469</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0474</v>
+        <v>0.4718</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4602</v>
+        <v>0.8424</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9347</v>
+        <v>0.4876</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4744</v>
+        <v>0.3547</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0172</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
         <v>-0.8363</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8535</v>
+        <v>0.7863</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4766</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2618</v>
+        <v>0.1946</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3286</v>
+        <v>0.2614</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0095</v>
+        <v>-0.3197</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3786</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3881</v>
+        <v>0.22</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5097</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9651</v>
+        <v>0.6359</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4876</v>
+        <v>0.3264</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4775</v>
+        <v>0.3095</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7199</v>
+        <v>-0.8661</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1721</v>
+        <v>-0.621</v>
       </c>
       <c r="F11" t="n">
-        <v>4.4522</v>
+        <v>-0.2451</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9873</v>
+        <v>-0.6133</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0742</v>
+        <v>-2.36</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08690000000000001</v>
+        <v>1.7467</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7996</v>
+        <v>-1.206</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-1.9053</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7127</v>
+        <v>0.6993</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7869</v>
+        <v>0.5927</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1611</v>
+        <v>-0.4547</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6258</v>
+        <v>1.0474</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.9432</v>
+        <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.7988</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1637</v>
+        <v>0.4973</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3541</v>
+        <v>0.9045</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8096</v>
+        <v>-0.4072</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W11" t="n">
         <v>1.0722</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.762</v>
+        <v>-0.906</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0737</v>
+        <v>-4.7868</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3116</v>
+        <v>3.8809</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6579</v>
+        <v>0.9873</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3434</v>
+        <v>1.0742</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3145</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7829</v>
+        <v>-0.7996</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0035</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7863</v>
+        <v>-0.7127</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1249</v>
+        <v>1.7869</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3469</v>
+        <v>1.1611</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4718</v>
+        <v>0.6258</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.232</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.232</v>
+        <v>-5.7988</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1278</v>
+        <v>0.9777</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0589</v>
+        <v>0.7393</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1867</v>
+        <v>0.2383</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4402</v>
+        <v>-2.1557</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1049</v>
+        <v>-2.7196</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6647</v>
+        <v>0.5639</v>
       </c>
       <c r="G13" t="n">
         <v>-3.4422</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5381</v>
+        <v>0.8226</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2794</v>
+        <v>0.6647</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2588</v>
+        <v>0.1579</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>29.3927</v>
+        <v>30.5131</v>
       </c>
       <c r="E14" t="n">
-        <v>5.278699999999995</v>
+        <v>6.398899999999998</v>
       </c>
       <c r="F14" t="n">
         <v>24.1141</v>
@@ -1516,19 +1516,19 @@
         <v>11.3861</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001999999999995339</v>
+        <v>0.0001999999999990898</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2581</v>
+        <v>3.258100000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.692200000000001</v>
+        <v>7.692199999999999</v>
       </c>
       <c r="L14" t="n">
         <v>-4.4341</v>
       </c>
       <c r="M14" t="n">
-        <v>8.128</v>
+        <v>8.128000000000002</v>
       </c>
       <c r="N14" t="n">
         <v>3.694</v>
@@ -1546,13 +1546,13 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>6.800299999999999</v>
+        <v>7.9207</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9141</v>
+        <v>5.034199999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8863</v>
+        <v>2.8862</v>
       </c>
       <c r="V14" t="n">
         <v>7.726799999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0747</v>
+        <v>1.7145</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0526</v>
+        <v>0.1089</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0222</v>
+        <v>1.6056</v>
       </c>
       <c r="G15" t="n">
         <v>0.2165</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0026</v>
+        <v>-0.3576</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3293</v>
+        <v>0.3857</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3267</v>
+        <v>-0.7433</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. RYAN</t>
+          <t>A. AVRAMOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.3404</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3398</v>
+        <v>-1.4899</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2465</v>
+        <v>1.8303</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5133</v>
+        <v>0.1223</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3266</v>
+        <v>-0.3963</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8399</v>
+        <v>0.5187</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7527</v>
+        <v>-0.1131</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0336</v>
+        <v>0.0476</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7863</v>
+        <v>-0.1607</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2395</v>
+        <v>0.2354</v>
       </c>
       <c r="N16" t="n">
-        <v>0.293</v>
+        <v>-0.4439</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0535</v>
+        <v>0.6793</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.188</v>
+        <v>-1.2432</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4129</v>
+        <v>-0.9825</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2249</v>
+        <v>-0.2607</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. AVRAMOVIC</t>
+          <t>M. RYAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1371</v>
+        <v>-0.2734</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8438</v>
+        <v>-0.8116</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7066</v>
+        <v>0.5382</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1223</v>
+        <v>-0.5133</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3963</v>
+        <v>0.3266</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5187</v>
+        <v>-0.8399</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1131</v>
+        <v>-0.7527</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0476</v>
+        <v>0.0336</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1607</v>
+        <v>-0.7863</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2354</v>
+        <v>0.2395</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4439</v>
+        <v>0.293</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6793</v>
+        <v>-0.0535</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7207</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3364</v>
+        <v>-0.0589</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3844</v>
+        <v>0.0668</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3378</v>
+        <v>-1.611</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.9646</v>
+        <v>-3.8467</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6269</v>
+        <v>2.2357</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2093</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0365</v>
+        <v>-0.2368</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4674</v>
+        <v>-0.3495</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5039</v>
+        <v>0.1127</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7886</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3565</v>
+        <v>-1.7395</v>
       </c>
       <c r="E19" t="n">
         <v>-2.1914</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1651</v>
+        <v>0.4519</v>
       </c>
       <c r="G19" t="n">
         <v>-0.342</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8701</v>
+        <v>-1.2531</v>
       </c>
       <c r="T19" t="n">
         <v>-1.0455</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8246</v>
+        <v>-0.2076</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.644</v>
+        <v>-3.0779</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8278</v>
+        <v>-2.0829</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4718</v>
+        <v>-0.995</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7677</v>
+        <v>-1.5929</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6808</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.9603</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1513</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0504</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.919</v>
+        <v>-0.8938</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7584</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1605</v>
+        <v>-0.2108</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6445</v>
+        <v>-0.3253</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6765</v>
+        <v>-0.224</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0321</v>
+        <v>-0.1013</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1115</v>
+        <v>-3.2782</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0829</v>
+        <v>-2.5724</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0286</v>
+        <v>-0.7058</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5929</v>
+        <v>-1.6665</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.917</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9603</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.5795</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0504</v>
+        <v>-0.1478</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.4317</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8938</v>
+        <v>-1.087</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7692</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2108</v>
+        <v>-0.3178</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3589</v>
+        <v>-0.3075</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.224</v>
+        <v>-0.8331</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1349</v>
+        <v>0.5256</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6213</v>
+        <v>-3.2952</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9262</v>
+        <v>0.1201</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.695</v>
+        <v>-3.4153</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6665</v>
+        <v>-0.7677</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.917</v>
+        <v>-0.6808</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5795</v>
+        <v>0.1513</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1478</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4317</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.087</v>
+        <v>-0.919</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7692</v>
+        <v>-0.7584</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3178</v>
+        <v>-0.1605</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6506</v>
+        <v>-0.0068</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.187</v>
+        <v>-0.0312</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5364</v>
+        <v>0.0244</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-3.2166</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6617</v>
+        <v>-3.5729</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6289</v>
+        <v>-3.1571</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0327</v>
+        <v>-0.4157</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9442</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0037</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6994</v>
+        <v>-0.2276</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3043</v>
+        <v>-0.6873</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9449</v>
+        <v>-5.9221</v>
       </c>
       <c r="E24" t="n">
         <v>-4.4723</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4726</v>
+        <v>-1.4498</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0673</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3154</v>
+        <v>0.3383</v>
       </c>
       <c r="T24" t="n">
         <v>0.6097</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2943</v>
+        <v>-0.2715</v>
       </c>
       <c r="V24" t="n">
         <v>0.6778999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.5593</v>
+        <v>-6.3183</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0805</v>
+        <v>-4.2548</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4788</v>
+        <v>-2.0635</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6219</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3834</v>
+        <v>-0.1423</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.955</v>
+        <v>-0.1294</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4283</v>
+        <v>-0.013</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0026</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-29.3927</v>
+        <v>-27.0336</v>
       </c>
       <c r="E26" t="n">
-        <v>-24.65</v>
+        <v>-24.6501</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.7424</v>
+        <v>-2.3834</v>
       </c>
       <c r="G26" t="n">
         <v>-11.3863</v>
@@ -2461,10 +2461,10 @@
         <v>-3.6939</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.434100000000001</v>
+        <v>-4.434099999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.2581</v>
+        <v>-3.258100000000001</v>
       </c>
       <c r="N26" t="n">
         <v>-7.6922</v>
@@ -2482,13 +2482,13 @@
         <v>12.7575</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.8004</v>
+        <v>-4.441199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.8863</v>
+        <v>-2.886299999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.9142</v>
+        <v>-1.5552</v>
       </c>
       <c r="V26" t="n">
         <v>-7.726800000000001</v>
